--- a/VALIDATION/CAS SFS01/Cas SFS01.xlsx
+++ b/VALIDATION/CAS SFS01/Cas SFS01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAID 1\LOGICIELS\CTICM AM - POUTRE MIXTE\DEV23\VALIDATION\CAS SFS01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228E1484-B7B9-47DA-BBAD-3C725E6F9B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA1EDE0-76A7-4E73-8EC1-F1015F87B3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -761,10 +761,10 @@
     <t>VM</t>
   </si>
   <si>
-    <t>Gy</t>
-  </si>
-  <si>
     <t>VplRd</t>
+  </si>
+  <si>
+    <t>GammaY</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1072,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1323,6 +1323,9 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1658,7 +1661,7 @@
       <c r="H6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="71">
+      <c r="I6" s="103">
         <f>D60</f>
         <v>16.426709395751477</v>
       </c>
@@ -2066,8 +2069,8 @@
         <v>10176679.093629118</v>
       </c>
       <c r="S20" s="78">
-        <f>dW^3*tw/12</f>
-        <v>9090347.2931333352</v>
+        <f>hw^3*tw/12</f>
+        <v>12794415.163133336</v>
       </c>
     </row>
     <row r="21" spans="3:23" x14ac:dyDescent="0.25">
@@ -2218,7 +2221,7 @@
       </c>
       <c r="S24" s="28">
         <f>SUM(S18:S23)</f>
-        <v>9206877.2431333344</v>
+        <v>12910945.113133335</v>
       </c>
     </row>
     <row r="25" spans="3:23" x14ac:dyDescent="0.25">
@@ -2305,14 +2308,14 @@
       </c>
       <c r="Q27" s="55">
         <f>IncertieCM/(ABS(hb-zG))*10</f>
-        <v>634.71237647493035</v>
+        <v>651.41790217299649</v>
       </c>
       <c r="R27" t="s">
         <v>71</v>
       </c>
       <c r="S27" s="82">
         <f>Q27*355/1000</f>
-        <v>225.32289364860026</v>
+        <v>231.25335527141374</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>147</v>
@@ -2340,7 +2343,7 @@
       </c>
       <c r="N28" s="49">
         <f>SUM(R24:S24)</f>
-        <v>140732938.48300132</v>
+        <v>144437006.35300133</v>
       </c>
       <c r="O28" t="s">
         <v>37</v>
@@ -2350,14 +2353,14 @@
       </c>
       <c r="Q28" s="55">
         <f>IncertieCM/(ABS(zG))*10</f>
-        <v>1797.9779664204714</v>
+        <v>1845.3004517474615</v>
       </c>
       <c r="R28" t="s">
         <v>71</v>
       </c>
       <c r="S28" s="82">
         <f t="shared" ref="S28:S29" si="3">Q28*355/1000</f>
-        <v>638.2821780792674</v>
+        <v>655.0816603703488</v>
       </c>
       <c r="U28" s="3" t="s">
         <v>149</v>
@@ -2382,7 +2385,7 @@
       </c>
       <c r="N29" s="9">
         <f>N28/10^4</f>
-        <v>14073.293848300133</v>
+        <v>14443.700635300132</v>
       </c>
       <c r="O29" t="s">
         <v>38</v>
@@ -2392,14 +2395,14 @@
       </c>
       <c r="Q29" s="55">
         <f>IncertieCM/(ABS(zG+Pl_t))*10</f>
-        <v>1508.8299793958131</v>
+        <v>1548.5421371054163</v>
       </c>
       <c r="R29" t="s">
         <v>71</v>
       </c>
       <c r="S29" s="82">
         <f t="shared" si="3"/>
-        <v>535.63464268551354</v>
+        <v>549.73245867242281</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>148</v>
@@ -2430,7 +2433,7 @@
       </c>
       <c r="Q30" s="83" cm="1">
         <f t="array" ref="Q30">MIN(Q27*FyS,Q28*FyI,Q29*FyPl)/1000/GammaM0</f>
-        <v>225.32289364860026</v>
+        <v>231.25335527141374</v>
       </c>
       <c r="R30" t="s">
         <v>18</v>
@@ -3097,7 +3100,7 @@
       <c r="C62" s="3"/>
       <c r="D62" s="4"/>
       <c r="P62" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q62" s="83">
         <f>V26*FyW/SQRT(3)/1000/GammaM0</f>
@@ -3369,7 +3372,7 @@
       </c>
       <c r="N85" s="54">
         <f>5/384*qG*LL^4/(E*IncertieCM/100)*1000^2</f>
-        <v>9.3794917367309232</v>
+        <v>9.1389559152251394</v>
       </c>
       <c r="O85" t="s">
         <v>2</v>
@@ -3381,7 +3384,7 @@
       </c>
       <c r="N86" s="54">
         <f>5/384*qQ_1*LL^4/(E*IncertieCM/100)*1000^2</f>
-        <v>11.419806013195544</v>
+        <v>11.126946602694259</v>
       </c>
       <c r="O86" t="s">
         <v>2</v>
@@ -3416,7 +3419,7 @@
       </c>
       <c r="N89" s="54">
         <f>N85+N86+Psi_0*N87</f>
-        <v>20.799297749926467</v>
+        <v>20.2659025179194</v>
       </c>
       <c r="O89" t="s">
         <v>2</v>
@@ -3579,7 +3582,7 @@
       </c>
       <c r="N101" s="54">
         <f>1/2/PI()*SQRT(PI()^4*(E*IncertieCM/100)/N97/LL^3)</f>
-        <v>5.1982863605387521</v>
+        <v>5.2662510823644419</v>
       </c>
       <c r="O101" t="s">
         <v>118</v>
@@ -3753,7 +3756,7 @@
       </c>
       <c r="E125" s="55">
         <f>VEd_U1*(MStatS/IncertieCM)*100</f>
-        <v>130.17742958621196</v>
+        <v>126.83904667102597</v>
       </c>
       <c r="G125">
         <f>Fu</f>
@@ -3766,7 +3769,7 @@
       </c>
       <c r="E126" s="55">
         <f>VEd_U2*(MStatS/IncertieCM)*100</f>
-        <v>107.72274599617056</v>
+        <v>104.96021046329331</v>
       </c>
       <c r="F126" t="s">
         <v>7</v>
@@ -3789,7 +3792,7 @@
       </c>
       <c r="E129" s="53">
         <f>E125/Fu*GammaM2*SQRT(3)/2*BetaW</f>
-        <v>0.26984910882690849</v>
+        <v>0.26292886422345124</v>
       </c>
     </row>
     <row r="130" spans="3:6" x14ac:dyDescent="0.25">
@@ -3798,7 +3801,7 @@
       </c>
       <c r="E130" s="53">
         <f>E126/Fu*GammaM2*SQRT(3)/2*BetaW</f>
-        <v>0.22330205089971253</v>
+        <v>0.2175754994228615</v>
       </c>
       <c r="F130" t="s">
         <v>2</v>
@@ -3927,23 +3930,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10702E5E-ED8A-4120-9F0B-C4375CB5FF62}">
-  <dimension ref="C2:J33"/>
+  <dimension ref="C2:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>183</v>
       </c>
@@ -3960,7 +3963,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C7" s="4">
         <v>1</v>
       </c>
@@ -3970,20 +3973,23 @@
       </c>
       <c r="E7" s="86">
         <f t="shared" ref="E7:E12" si="0">1/(InertieY_MM4)*((zG-D7))*(10^3)</f>
-        <v>-1.5755167806145618E-3</v>
+        <v>-1.5351128617500458E-3</v>
       </c>
       <c r="F7" s="85">
         <f t="shared" ref="F7:F12" si="1">MEd_U1*E7*1000</f>
-        <v>-369.91914492542429</v>
+        <v>-360.4326175193703</v>
       </c>
       <c r="G7" s="73">
         <f t="shared" ref="G7:G12" si="2">ABS(F7/(FyS/GammaM0))</f>
-        <v>1.0420257603533079</v>
+        <v>1.0153031479418881</v>
       </c>
       <c r="I7" s="82"/>
       <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>-113.47</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C8" s="4">
         <v>2</v>
       </c>
@@ -3993,18 +3999,21 @@
       </c>
       <c r="E8" s="86">
         <f t="shared" si="0"/>
-        <v>-1.4994862499133755E-3</v>
+        <v>-1.4610321239241081E-3</v>
       </c>
       <c r="F8" s="85">
         <f t="shared" si="1"/>
-        <v>-352.06776482508781</v>
+        <v>-343.03903369392481</v>
       </c>
       <c r="G8" s="73">
         <f t="shared" si="2"/>
-        <v>0.99174018260588115</v>
-      </c>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+        <v>0.96630713716598537</v>
+      </c>
+      <c r="K8">
+        <v>-138.15</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" s="4">
         <v>3</v>
       </c>
@@ -4024,8 +4033,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="K9">
+        <f>1.35*K7+1.5*K8</f>
+        <v>-360.40950000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" s="4">
         <v>4</v>
       </c>
@@ -4035,18 +4048,22 @@
       </c>
       <c r="E10" s="86">
         <f t="shared" si="0"/>
-        <v>4.8014981114742009E-4</v>
+        <v>4.6783643292694458E-4</v>
       </c>
       <c r="F10" s="85">
         <f t="shared" si="1"/>
-        <v>112.73545909582423</v>
+        <v>109.84437320038558</v>
       </c>
       <c r="G10" s="73">
         <f t="shared" si="2"/>
-        <v>0.31756467350936401</v>
-      </c>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+        <v>0.30942076957855091</v>
+      </c>
+      <c r="K10">
+        <f>InertieY_MM4</f>
+        <v>144437006.35300133</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C11" s="4">
         <v>5</v>
       </c>
@@ -4055,18 +4072,18 @@
       </c>
       <c r="E11" s="86">
         <f t="shared" si="0"/>
-        <v>5.5618034184860647E-4</v>
+        <v>5.4191717075288237E-4</v>
       </c>
       <c r="F11" s="85">
         <f t="shared" si="1"/>
-        <v>130.58683919616075</v>
+        <v>127.23795702583109</v>
       </c>
       <c r="G11" s="73">
         <f t="shared" si="2"/>
-        <v>0.36785025125679083</v>
-      </c>
-    </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+        <v>0.35841678035445379</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C12" s="4">
         <v>6</v>
       </c>
@@ -4076,30 +4093,30 @@
       </c>
       <c r="E12" s="86">
         <f t="shared" si="0"/>
-        <v>6.6276519797176491E-4</v>
+        <v>6.4576867237802881E-4</v>
       </c>
       <c r="F12" s="85">
         <f t="shared" si="1"/>
-        <v>155.61213840224002</v>
+        <v>151.62148575309118</v>
       </c>
       <c r="G12" s="73">
         <f t="shared" si="2"/>
-        <v>0.43834405183729586</v>
-      </c>
-    </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+        <v>0.42710277676927094</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>189</v>
       </c>
@@ -4110,7 +4127,7 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
@@ -4190,7 +4207,7 @@
         <v>201</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
@@ -4199,7 +4216,7 @@
       </c>
       <c r="D28" s="62">
         <f>F10</f>
-        <v>112.73545909582423</v>
+        <v>109.84437320038558</v>
       </c>
       <c r="E28" s="73">
         <f>+D24</f>
@@ -4210,11 +4227,11 @@
       </c>
       <c r="G28" s="85">
         <f>SQRT(D28^2+E28^2-D28*E28+3*F28^2)</f>
-        <v>99.824826783782314</v>
+        <v>97.696594034657494</v>
       </c>
       <c r="H28" s="85">
         <f t="shared" ref="H28:H33" si="3">G28/(FyS/GammaM0)</f>
-        <v>0.28119669516558399</v>
+        <v>0.27520167333706336</v>
       </c>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.25">
@@ -4223,22 +4240,22 @@
       </c>
       <c r="D29" s="62">
         <f>AVERAGE(D28,D30)</f>
-        <v>121.66114914599248</v>
+        <v>118.54116511310833</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
       </c>
       <c r="F29" s="82">
-        <f>3/2*qELU/tf</f>
-        <v>7.314400609943621</v>
+        <f>3/2*qELU/tf/2</f>
+        <v>3.6572003049718105</v>
       </c>
       <c r="G29" s="85">
         <f t="shared" ref="G29:G33" si="4">SQRT(D29^2+E29^2-D29*E29+3*F29^2)</f>
-        <v>122.31899517397801</v>
+        <v>118.7102909127312</v>
       </c>
       <c r="H29" s="85">
         <f t="shared" si="3"/>
-        <v>0.34456054978585354</v>
+        <v>0.33439518566966536</v>
       </c>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.25">
@@ -4247,7 +4264,7 @@
       </c>
       <c r="D30" s="62">
         <f>F11</f>
-        <v>130.58683919616075</v>
+        <v>127.23795702583109</v>
       </c>
       <c r="E30" s="73">
         <f>-E28</f>
@@ -4258,11 +4275,11 @@
       </c>
       <c r="G30" s="85">
         <f t="shared" si="4"/>
-        <v>181.89987288203781</v>
+        <v>178.78948964749171</v>
       </c>
       <c r="H30" s="85">
         <f t="shared" si="3"/>
-        <v>0.5123940081184164</v>
+        <v>0.50363236520420196</v>
       </c>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
@@ -4271,7 +4288,7 @@
       </c>
       <c r="D31" s="62">
         <f>F11</f>
-        <v>130.58683919616075</v>
+        <v>127.23795702583109</v>
       </c>
       <c r="E31" s="73">
         <f>D20</f>
@@ -4282,11 +4299,11 @@
       </c>
       <c r="G31" s="85">
         <f t="shared" si="4"/>
-        <v>118.77655454602653</v>
+        <v>115.50548941581434</v>
       </c>
       <c r="H31" s="85">
         <f t="shared" si="3"/>
-        <v>0.33458184379162403</v>
+        <v>0.32536757581919534</v>
       </c>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.25">
@@ -4295,22 +4312,22 @@
       </c>
       <c r="D32" s="62">
         <f>AVERAGE(D31,D33)</f>
-        <v>143.0994887992004</v>
+        <v>139.42972138946112</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
       </c>
       <c r="F32" s="73">
-        <f>3/2*qELU/Pl_t</f>
-        <v>5.2176057684264494</v>
+        <f>3/2*qELU/Pl_t/2</f>
+        <v>2.6088028842132247</v>
       </c>
       <c r="G32" s="85">
         <f t="shared" si="4"/>
-        <v>143.38456654904192</v>
+        <v>139.50292027125738</v>
       </c>
       <c r="H32" s="85">
         <f t="shared" si="3"/>
-        <v>0.40390018746208994</v>
+        <v>0.3929659725950912</v>
       </c>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.25">
@@ -4319,7 +4336,7 @@
       </c>
       <c r="D33" s="62">
         <f>F12</f>
-        <v>155.61213840224002</v>
+        <v>151.62148575309118</v>
       </c>
       <c r="E33" s="73">
         <f>-E31</f>
@@ -4330,11 +4347,11 @@
       </c>
       <c r="G33" s="85">
         <f t="shared" si="4"/>
-        <v>171.94780746624863</v>
+        <v>168.00092252810995</v>
       </c>
       <c r="H33" s="85">
         <f t="shared" si="3"/>
-        <v>0.48436002103168629</v>
+        <v>0.47324203529045056</v>
       </c>
     </row>
   </sheetData>

--- a/VALIDATION/CAS SFS01/Cas SFS01.xlsx
+++ b/VALIDATION/CAS SFS01/Cas SFS01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAID 1\LOGICIELS\CTICM AM - POUTRE MIXTE\DEV23\VALIDATION\CAS SFS01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA1EDE0-76A7-4E73-8EC1-F1015F87B3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C461F26-74CB-4C45-A6B3-57D5A8C1CD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,8 @@
   <definedNames>
     <definedName name="A">Feuil1!$N$26</definedName>
     <definedName name="Ac">Feuil1!$D$53</definedName>
-    <definedName name="Alpha">Feuil1!$D$79</definedName>
-    <definedName name="AlphaLT">Feuil1!$E$136</definedName>
+    <definedName name="Alpha">Feuil1!#REF!</definedName>
+    <definedName name="AlphaLT">Feuil1!#REF!</definedName>
     <definedName name="Bac_bb">Feuil1!$D$35</definedName>
     <definedName name="Bac_bm">Feuil1!$D$40</definedName>
     <definedName name="Bac_bt">Feuil1!$D$36</definedName>
@@ -31,7 +31,7 @@
     <definedName name="Bac_Mu">Feuil1!$D$39</definedName>
     <definedName name="Bac_t">Feuil1!$D$37</definedName>
     <definedName name="bAppMin">Feuil1!$D$41</definedName>
-    <definedName name="BetaW">Feuil1!$E$127</definedName>
+    <definedName name="BetaW">Feuil1!#REF!</definedName>
     <definedName name="bf">Feuil1!$D$6</definedName>
     <definedName name="d_1">Feuil1!$D$28</definedName>
     <definedName name="d_2">Feuil1!$D$29</definedName>
@@ -40,17 +40,17 @@
     <definedName name="dp">'Section élastique'!$D$19</definedName>
     <definedName name="dW">Feuil1!$D$9</definedName>
     <definedName name="E">Feuil1!$D$27</definedName>
-    <definedName name="Elan">Feuil1!$D$77</definedName>
-    <definedName name="ElancementW">Feuil1!$E$107</definedName>
-    <definedName name="EpsilonW">Feuil1!$D$80</definedName>
-    <definedName name="Eta">Feuil1!$E$108</definedName>
+    <definedName name="Elan">Feuil1!#REF!</definedName>
+    <definedName name="ElancementW">Feuil1!#REF!</definedName>
+    <definedName name="EpsilonW">Feuil1!#REF!</definedName>
+    <definedName name="Eta">Feuil1!#REF!</definedName>
     <definedName name="F_Q2">Feuil1!$I$8</definedName>
     <definedName name="Fu">Feuil1!$D$21</definedName>
     <definedName name="FyI">Feuil1!$D$19</definedName>
     <definedName name="FyPl">Feuil1!$D$20</definedName>
     <definedName name="FyS">Feuil1!$D$17</definedName>
     <definedName name="FyW">Feuil1!$D$18</definedName>
-    <definedName name="g">Feuil1!$N$93</definedName>
+    <definedName name="g">Feuil1!$N$79</definedName>
     <definedName name="GammaG">Feuil1!$N$6</definedName>
     <definedName name="GammaM0">Feuil1!$N$8</definedName>
     <definedName name="GammaM1">Feuil1!$N$9</definedName>
@@ -63,15 +63,15 @@
     <definedName name="InertieY_MM4">Feuil1!$N$28</definedName>
     <definedName name="kcG">Feuil1!$W$6</definedName>
     <definedName name="kcI">Feuil1!$W$7</definedName>
-    <definedName name="KhiLT">Feuil1!$E$138</definedName>
-    <definedName name="KhiW">Feuil1!$E$114</definedName>
-    <definedName name="kTau">Feuil1!$E$112</definedName>
-    <definedName name="LambdaLT">Feuil1!$E$135</definedName>
-    <definedName name="LambdaW">Feuil1!$E$113</definedName>
+    <definedName name="KhiLT">Feuil1!#REF!</definedName>
+    <definedName name="KhiW">Feuil1!#REF!</definedName>
+    <definedName name="kTau">Feuil1!#REF!</definedName>
+    <definedName name="LambdaLT">Feuil1!#REF!</definedName>
+    <definedName name="LambdaW">Feuil1!#REF!</definedName>
     <definedName name="listeNbAppuis">Param!$I$7:$I$10</definedName>
     <definedName name="LL">Feuil1!$D$25</definedName>
     <definedName name="MatriceRa">Param!$I$7:$J$10</definedName>
-    <definedName name="Mcr">Feuil1!$E$134</definedName>
+    <definedName name="Mcr">Feuil1!#REF!</definedName>
     <definedName name="MEd_Q1">Feuil1!$J$15</definedName>
     <definedName name="MEd_Q2">Feuil1!$J$17</definedName>
     <definedName name="MEd_U1">Feuil1!$J$23</definedName>
@@ -79,34 +79,34 @@
     <definedName name="MEdG">Feuil1!$J$13</definedName>
     <definedName name="MelRd">Feuil1!$Q$30</definedName>
     <definedName name="MplRd">Feuil1!$Q$61</definedName>
-    <definedName name="MRd">Feuil1!$E$94</definedName>
-    <definedName name="MStatS">Feuil1!$E$123</definedName>
+    <definedName name="MRd">Feuil1!#REF!</definedName>
+    <definedName name="MStatS">Feuil1!#REF!</definedName>
     <definedName name="non">Param!$C$3</definedName>
     <definedName name="oui">Param!$C$2</definedName>
     <definedName name="pANP">Feuil1!$N$47</definedName>
-    <definedName name="PhiLT">Feuil1!$E$137</definedName>
+    <definedName name="PhiLT">Feuil1!#REF!</definedName>
     <definedName name="Pl_b">Feuil1!$D$13</definedName>
     <definedName name="Pl_t">Feuil1!$D$14</definedName>
-    <definedName name="Psi">Feuil1!$D$85</definedName>
+    <definedName name="Psi">Feuil1!#REF!</definedName>
     <definedName name="Psi_0">Feuil1!$N$10</definedName>
     <definedName name="pW">Feuil1!$N$57</definedName>
     <definedName name="qELU">Feuil1!$J$30</definedName>
     <definedName name="qG">Feuil1!$I$6</definedName>
     <definedName name="qQ_1">Feuil1!$I$7</definedName>
-    <definedName name="RhoA">Feuil1!$N$72</definedName>
+    <definedName name="RhoA">Feuil1!#REF!</definedName>
     <definedName name="rhoC">Feuil1!$D$51</definedName>
     <definedName name="rr">Feuil1!$D$11</definedName>
     <definedName name="tc">Feuil1!$D$46</definedName>
     <definedName name="td">Feuil1!$D$45</definedName>
     <definedName name="tf">Feuil1!$D$7</definedName>
     <definedName name="tw">Feuil1!$D$10</definedName>
-    <definedName name="VbRd">Feuil1!$E$115</definedName>
+    <definedName name="VbRd">Feuil1!#REF!</definedName>
     <definedName name="VEd_Q1">Feuil1!$J$16</definedName>
     <definedName name="VEd_Q2">Feuil1!$J$18</definedName>
     <definedName name="VEd_U1">Feuil1!$J$24</definedName>
     <definedName name="VEd_U2">Feuil1!$J$26</definedName>
     <definedName name="VEdG">Feuil1!$J$14</definedName>
-    <definedName name="VRd">Feuil1!$E$100</definedName>
+    <definedName name="VRd">Feuil1!#REF!</definedName>
     <definedName name="zANP">Feuil1!$N$48</definedName>
     <definedName name="zG">Feuil1!$N$27</definedName>
   </definedNames>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="162">
   <si>
     <t>hw</t>
   </si>
@@ -311,57 +311,18 @@
     <t>MplRd</t>
   </si>
   <si>
-    <t>Classe de l'âme en flexion</t>
-  </si>
-  <si>
     <t>c/t</t>
   </si>
   <si>
-    <t>Limite classe 1</t>
-  </si>
-  <si>
-    <t>cc</t>
-  </si>
-  <si>
-    <t>Alpha</t>
-  </si>
-  <si>
-    <t>Limite Classe 2</t>
-  </si>
-  <si>
-    <t>Limite Classe 3</t>
-  </si>
-  <si>
-    <t>EpsilonW</t>
-  </si>
-  <si>
-    <t>Psi</t>
-  </si>
-  <si>
     <t>Classe de l'âme</t>
   </si>
   <si>
     <t>ELU</t>
   </si>
   <si>
-    <t>Flexion</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>GammaM</t>
   </si>
   <si>
-    <t>MRd</t>
-  </si>
-  <si>
     <t>Welfs</t>
   </si>
   <si>
@@ -374,87 +335,18 @@
     <t>MelRd</t>
   </si>
   <si>
-    <t>Tranchant</t>
-  </si>
-  <si>
-    <t>VRd</t>
-  </si>
-  <si>
-    <t>Voilement par cisaillement</t>
-  </si>
-  <si>
-    <t>hw/tw</t>
-  </si>
-  <si>
-    <t>Eta</t>
-  </si>
-  <si>
-    <t>72 Epsilon/Eta</t>
-  </si>
-  <si>
-    <t>Vérification requise ?</t>
-  </si>
-  <si>
-    <t>kTau</t>
-  </si>
-  <si>
-    <t>LambdaW</t>
-  </si>
-  <si>
-    <t>KhiW</t>
-  </si>
-  <si>
-    <t>VbRd</t>
-  </si>
-  <si>
-    <t>GVb</t>
-  </si>
-  <si>
-    <t>Soudures</t>
-  </si>
-  <si>
-    <t>Moment stat Semelle sup</t>
-  </si>
-  <si>
-    <t>Flux de cisaillement</t>
-  </si>
-  <si>
-    <t>ELU1</t>
-  </si>
-  <si>
-    <t>ELU2</t>
-  </si>
-  <si>
     <t>Fu</t>
   </si>
   <si>
     <t>GammaM2</t>
   </si>
   <si>
-    <t>aw mini</t>
-  </si>
-  <si>
-    <t>BetaW</t>
-  </si>
-  <si>
-    <t>Autres propriétés</t>
-  </si>
-  <si>
     <t>Av</t>
   </si>
   <si>
     <t>Inertie Y</t>
   </si>
   <si>
-    <t>Inertie Z</t>
-  </si>
-  <si>
-    <t>mlin</t>
-  </si>
-  <si>
-    <t>Rho</t>
-  </si>
-  <si>
     <t>kg/m</t>
   </si>
   <si>
@@ -464,18 +356,9 @@
     <t>kg</t>
   </si>
   <si>
-    <t>Surface de peinture totale</t>
-  </si>
-  <si>
-    <t>Périmètre</t>
-  </si>
-  <si>
     <t>m2</t>
   </si>
   <si>
-    <t>Surface peinture - face sup</t>
-  </si>
-  <si>
     <t>Flèches</t>
   </si>
   <si>
@@ -518,30 +401,6 @@
     <t>FELU</t>
   </si>
   <si>
-    <t>Déversement</t>
-  </si>
-  <si>
-    <t>Mcr</t>
-  </si>
-  <si>
-    <t>LambdaLT</t>
-  </si>
-  <si>
-    <t>PhiLT</t>
-  </si>
-  <si>
-    <t>AlphaLT</t>
-  </si>
-  <si>
-    <t>KhiLT</t>
-  </si>
-  <si>
-    <t>MbRd</t>
-  </si>
-  <si>
-    <t>GLT</t>
-  </si>
-  <si>
     <t>NtRd</t>
   </si>
   <si>
@@ -765,20 +624,34 @@
   </si>
   <si>
     <t>GammaY</t>
+  </si>
+  <si>
+    <t>GammaV</t>
+  </si>
+  <si>
+    <t>Hauteur d'âme comprimée</t>
+  </si>
+  <si>
+    <t>Epsilon</t>
+  </si>
+  <si>
+    <t>Limite classe 2</t>
+  </si>
+  <si>
+    <t>Classe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
     <numFmt numFmtId="168" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -802,16 +675,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -892,12 +757,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -911,6 +770,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1072,7 +943,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1196,46 +1067,27 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1269,7 +1121,7 @@
     <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1325,6 +1177,21 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1612,7 +1479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:W155"/>
+  <dimension ref="C1:W87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
@@ -1620,17 +1487,17 @@
   <sheetData>
     <row r="1" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -1650,7 +1517,7 @@
     </row>
     <row r="6" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="D6" s="6">
         <v>150</v>
@@ -1661,7 +1528,7 @@
       <c r="H6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="103">
+      <c r="I6" s="96">
         <f>D60</f>
         <v>16.426709395751477</v>
       </c>
@@ -1675,16 +1542,16 @@
         <v>1.35</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="W6" s="81">
+        <v>98</v>
+      </c>
+      <c r="W6" s="74">
         <f>(10-3*PI())/(12-3*PI())</f>
         <v>0.22336793894575216</v>
       </c>
     </row>
     <row r="7" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="D7" s="6">
         <v>10.7</v>
@@ -1708,7 +1575,7 @@
         <v>1.5</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="W7" s="6">
         <f>0.0151</f>
@@ -1744,7 +1611,7 @@
     </row>
     <row r="9" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C9" s="3" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="D9" s="8">
         <f>hb-2*tf-2*rr</f>
@@ -1779,7 +1646,7 @@
     </row>
     <row r="11" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="D11" s="6">
         <v>15</v>
@@ -1788,7 +1655,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="N11" s="6">
         <v>1.25</v>
@@ -1796,7 +1663,7 @@
     </row>
     <row r="12" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C12" s="3" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="D12" s="6">
         <v>300</v>
@@ -1813,7 +1680,7 @@
     </row>
     <row r="13" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C13" s="3" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="D13" s="6">
         <v>300</v>
@@ -1837,7 +1704,7 @@
     </row>
     <row r="14" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C14" s="3" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="D14" s="6">
         <v>15</v>
@@ -1849,7 +1716,7 @@
       <c r="I14" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="87">
+      <c r="J14" s="80">
         <f>qG*LL/2</f>
         <v>49.280128187254434</v>
       </c>
@@ -1979,19 +1846,19 @@
         <f>-tf/2+hb</f>
         <v>294.64999999999998</v>
       </c>
-      <c r="P18" s="79">
+      <c r="P18" s="72">
         <f t="shared" ref="P18:P23" si="0">N18*O18</f>
         <v>472913.24999999994</v>
       </c>
-      <c r="Q18" s="74">
+      <c r="Q18" s="67">
         <f t="shared" ref="Q18:Q23" si="1">O18-zG</f>
         <v>216.3771061651654</v>
       </c>
-      <c r="R18" s="76">
+      <c r="R18" s="69">
         <f t="shared" ref="R18:R23" si="2">N18*Q18^2</f>
         <v>75144578.576220065</v>
       </c>
-      <c r="S18" s="78">
+      <c r="S18" s="71">
         <f>bf*tf^3/12</f>
         <v>15313.037499999997</v>
       </c>
@@ -2008,13 +1875,13 @@
         <v>44</v>
       </c>
       <c r="M19" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="N19" s="75">
+        <v>95</v>
+      </c>
+      <c r="N19" s="68">
         <f>(4-PI())*rr^2/2</f>
         <v>96.57082647114828</v>
       </c>
-      <c r="O19" s="82">
+      <c r="O19" s="75">
         <f>hb-tf-kcG*rr</f>
         <v>285.94948091581375</v>
       </c>
@@ -2022,22 +1889,22 @@
         <f t="shared" si="0"/>
         <v>27614.377701035977</v>
       </c>
-      <c r="Q19" s="75">
+      <c r="Q19" s="68">
         <f t="shared" si="1"/>
         <v>207.67658708097917</v>
       </c>
-      <c r="R19" s="77">
+      <c r="R19" s="70">
         <f t="shared" si="2"/>
         <v>4165057.7201632154</v>
       </c>
-      <c r="S19" s="78">
+      <c r="S19" s="71">
         <f>kcI*rr^4</f>
         <v>764.4375</v>
       </c>
     </row>
     <row r="20" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="D20" s="6">
         <v>355</v>
@@ -2060,22 +1927,22 @@
         <f t="shared" si="0"/>
         <v>296709</v>
       </c>
-      <c r="Q20" s="75">
+      <c r="Q20" s="68">
         <f t="shared" si="1"/>
         <v>71.727106165165424</v>
       </c>
-      <c r="R20" s="77">
+      <c r="R20" s="70">
         <f t="shared" si="2"/>
         <v>10176679.093629118</v>
       </c>
-      <c r="S20" s="78">
+      <c r="S20" s="71">
         <f>hw^3*tw/12</f>
         <v>12794415.163133336</v>
       </c>
     </row>
     <row r="21" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C21" s="3" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D21" s="6">
         <v>470</v>
@@ -2090,13 +1957,13 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="M21" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="N21" s="75">
+        <v>96</v>
+      </c>
+      <c r="N21" s="68">
         <f>(4-PI())*rr^2/2</f>
         <v>96.57082647114828</v>
       </c>
-      <c r="O21" s="62">
+      <c r="O21" s="59">
         <f>tf+kcG*rr</f>
         <v>14.050519084186281</v>
       </c>
@@ -2104,15 +1971,15 @@
         <f t="shared" si="0"/>
         <v>1356.8702403085106</v>
       </c>
-      <c r="Q21" s="75">
+      <c r="Q21" s="68">
         <f t="shared" si="1"/>
         <v>-64.222374750648299</v>
       </c>
-      <c r="R21" s="77">
+      <c r="R21" s="70">
         <f t="shared" si="2"/>
         <v>398307.66962677037</v>
       </c>
-      <c r="S21" s="78">
+      <c r="S21" s="71">
         <f>kcI*rr^4</f>
         <v>764.4375</v>
       </c>
@@ -2129,19 +1996,19 @@
         <f>tf/2</f>
         <v>5.35</v>
       </c>
-      <c r="P22" s="78">
+      <c r="P22" s="71">
         <f t="shared" si="0"/>
         <v>8586.75</v>
       </c>
-      <c r="Q22" s="75">
+      <c r="Q22" s="68">
         <f t="shared" si="1"/>
         <v>-72.922893834834582</v>
       </c>
-      <c r="R22" s="77">
+      <c r="R22" s="70">
         <f t="shared" si="2"/>
         <v>8534986.2546207216</v>
       </c>
-      <c r="S22" s="78">
+      <c r="S22" s="71">
         <f>bf*tf^3/12</f>
         <v>15313.037499999997</v>
       </c>
@@ -2167,7 +2034,7 @@
         <v>18</v>
       </c>
       <c r="M23" s="41" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="N23" s="5">
         <f>Pl_b*Pl_t</f>
@@ -2207,7 +2074,7 @@
       <c r="K24" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="N24" s="80">
+      <c r="N24" s="73">
         <f>SUM(N18:N23)</f>
         <v>9881.2016529422981</v>
       </c>
@@ -2273,7 +2140,7 @@
         <v>36</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="V26" s="48">
         <f>SUM(N19:N21)+2*(2*rr+tw)*tf/2</f>
@@ -2285,7 +2152,7 @@
     </row>
     <row r="27" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C27" s="3" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="D27" s="6">
         <v>210000</v>
@@ -2304,33 +2171,33 @@
         <v>2</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="Q27" s="55">
         <f>IncertieCM/(ABS(hb-zG))*10</f>
         <v>651.41790217299649</v>
       </c>
       <c r="R27" t="s">
-        <v>71</v>
-      </c>
-      <c r="S27" s="82">
+        <v>58</v>
+      </c>
+      <c r="S27" s="75">
         <f>Q27*355/1000</f>
         <v>231.25335527141374</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="V27" s="48">
         <f>7850*A/10^6</f>
         <v>77.567432975597043</v>
       </c>
       <c r="W27" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C28" s="3" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="D28" s="6">
         <v>2</v>
@@ -2339,7 +2206,7 @@
         <v>21</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="N28" s="49">
         <f>SUM(R24:S24)</f>
@@ -2349,33 +2216,33 @@
         <v>37</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="Q28" s="55">
         <f>IncertieCM/(ABS(zG))*10</f>
         <v>1845.3004517474615</v>
       </c>
       <c r="R28" t="s">
-        <v>71</v>
-      </c>
-      <c r="S28" s="82">
+        <v>58</v>
+      </c>
+      <c r="S28" s="75">
         <f t="shared" ref="S28:S29" si="3">Q28*355/1000</f>
         <v>655.0816603703488</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="V28" s="9">
         <f>V27*LL</f>
         <v>465.40459785358223</v>
       </c>
       <c r="W28" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C29" s="3" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="D29" s="6">
         <v>2</v>
@@ -2391,21 +2258,21 @@
         <v>38</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="Q29" s="55">
         <f>IncertieCM/(ABS(zG+Pl_t))*10</f>
         <v>1548.5421371054163</v>
       </c>
       <c r="R29" t="s">
-        <v>71</v>
-      </c>
-      <c r="S29" s="82">
+        <v>58</v>
+      </c>
+      <c r="S29" s="75">
         <f t="shared" si="3"/>
         <v>549.73245867242281</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="V29" s="8">
         <f>604+Pl_b^3*Pl_t/12/10^4</f>
@@ -2419,7 +2286,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
       <c r="I30" s="3" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="J30" s="54">
         <f>GammaG*qG+GammaQ*(qQ_1)</f>
@@ -2429,9 +2296,9 @@
         <v>7</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q30" s="83" cm="1">
+        <v>59</v>
+      </c>
+      <c r="Q30" s="76" cm="1">
         <f t="array" ref="Q30">MIN(Q27*FyS,Q28*FyI,Q29*FyPl)/1000/GammaM0</f>
         <v>231.25335527141374</v>
       </c>
@@ -2441,13 +2308,13 @@
     </row>
     <row r="31" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C31" s="1" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="I31" s="3" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="J31" s="5">
         <f>Psi_0*GammaQ*F_Q2</f>
@@ -2472,7 +2339,7 @@
     </row>
     <row r="33" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C33" s="3" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="D33" s="6">
         <v>58</v>
@@ -2483,7 +2350,7 @@
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C34" s="3" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="D34" s="6">
         <v>207</v>
@@ -2498,21 +2365,21 @@
         <v>28</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>30</v>
       </c>
       <c r="R34" s="5" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C35" s="3" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="D35" s="6">
         <v>62</v>
@@ -2520,6 +2387,11 @@
       <c r="E35" t="s">
         <v>2</v>
       </c>
+      <c r="I35" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
       <c r="M35" s="41" t="s">
         <v>26</v>
       </c>
@@ -2531,7 +2403,7 @@
         <f>FyS/GammaM0</f>
         <v>355</v>
       </c>
-      <c r="P35" s="62">
+      <c r="P35" s="59">
         <f>N35*O35/1000</f>
         <v>569.77499999999998</v>
       </c>
@@ -2539,18 +2411,18 @@
         <f>O18</f>
         <v>294.64999999999998</v>
       </c>
-      <c r="R35" s="62">
+      <c r="R35" s="59">
         <f>P41-P35</f>
         <v>2938.0515867945151</v>
       </c>
-      <c r="S35" s="62">
+      <c r="S35" s="59">
         <f>P35</f>
         <v>569.77499999999998</v>
       </c>
     </row>
     <row r="36" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C36" s="3" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="D36" s="6">
         <v>101</v>
@@ -2558,10 +2430,17 @@
       <c r="E36" t="s">
         <v>2</v>
       </c>
+      <c r="I36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J36" s="52">
+        <f>MEd_U1/MplRd</f>
+        <v>0.78770634435695452</v>
+      </c>
       <c r="M36" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="N36" s="90">
+        <v>95</v>
+      </c>
+      <c r="N36" s="83">
         <f>N19+rr*tw</f>
         <v>203.07082647114828</v>
       </c>
@@ -2569,27 +2448,27 @@
         <f>FyW/GammaM0</f>
         <v>355</v>
       </c>
-      <c r="P36" s="62">
+      <c r="P36" s="59">
         <f t="shared" ref="P36:P40" si="4">N36*O36/1000</f>
         <v>72.090143397257634</v>
       </c>
-      <c r="Q36" s="82">
+      <c r="Q36" s="75">
         <f>(O19*(4-PI())*rr^2/2+(hb-tf-kcG*rr)*rr*tw)/N36</f>
         <v>285.94948091581375</v>
       </c>
-      <c r="R36" s="62">
+      <c r="R36" s="59">
         <f>R35-P36</f>
         <v>2865.9614433972574</v>
       </c>
-      <c r="S36" s="62">
+      <c r="S36" s="59">
         <f>S35+P36</f>
         <v>641.86514339725761</v>
       </c>
-      <c r="V36" s="89"/>
+      <c r="V36" s="82"/>
     </row>
     <row r="37" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C37" s="3" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="D37" s="6">
         <v>0.75</v>
@@ -2597,10 +2476,17 @@
       <c r="E37" t="s">
         <v>2</v>
       </c>
+      <c r="I37" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J37" s="52">
+        <f>VEd_U1/Q62</f>
+        <v>0.29737245800864787</v>
+      </c>
       <c r="M37" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="N37" s="63">
+      <c r="N37" s="60">
         <f>dW*tw</f>
         <v>1765.0600000000002</v>
       </c>
@@ -2608,7 +2494,7 @@
         <f>FyW/GammaM0</f>
         <v>355</v>
       </c>
-      <c r="P37" s="62">
+      <c r="P37" s="59">
         <f t="shared" si="4"/>
         <v>626.59630000000004</v>
       </c>
@@ -2616,18 +2502,18 @@
         <f t="shared" ref="Q37:Q40" si="5">O20</f>
         <v>150</v>
       </c>
-      <c r="R37" s="62">
+      <c r="R37" s="59">
         <f t="shared" ref="R37:R40" si="6">R36-P37</f>
         <v>2239.3651433972573</v>
       </c>
-      <c r="S37" s="62">
+      <c r="S37" s="59">
         <f t="shared" ref="S37:S40" si="7">S36+P37</f>
         <v>1268.4614433972577</v>
       </c>
     </row>
     <row r="38" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C38" s="3" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="D38" s="6">
         <v>355</v>
@@ -2636,9 +2522,9 @@
         <v>44</v>
       </c>
       <c r="M38" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="N38" s="90">
+        <v>96</v>
+      </c>
+      <c r="N38" s="83">
         <f>N36</f>
         <v>203.07082647114828</v>
       </c>
@@ -2646,37 +2532,37 @@
         <f>FyW/GammaM0</f>
         <v>355</v>
       </c>
-      <c r="P38" s="62">
+      <c r="P38" s="59">
         <f t="shared" si="4"/>
         <v>72.090143397257634</v>
       </c>
-      <c r="Q38" s="82">
+      <c r="Q38" s="75">
         <f>Q39+(Q35-Q36)</f>
         <v>14.050519084186226</v>
       </c>
-      <c r="R38" s="62">
+      <c r="R38" s="59">
         <f t="shared" si="6"/>
         <v>2167.2749999999996</v>
       </c>
-      <c r="S38" s="62">
+      <c r="S38" s="59">
         <f t="shared" si="7"/>
         <v>1340.5515867945153</v>
       </c>
     </row>
     <row r="39" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C39" s="3" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="D39" s="6">
         <v>11.37</v>
       </c>
       <c r="E39" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="M39" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="N39" s="63">
+      <c r="N39" s="60">
         <f>N22</f>
         <v>1605</v>
       </c>
@@ -2684,7 +2570,7 @@
         <f>FyI/GammaM0</f>
         <v>355</v>
       </c>
-      <c r="P39" s="62">
+      <c r="P39" s="59">
         <f t="shared" si="4"/>
         <v>569.77499999999998</v>
       </c>
@@ -2692,18 +2578,18 @@
         <f t="shared" si="5"/>
         <v>5.35</v>
       </c>
-      <c r="R39" s="62">
+      <c r="R39" s="59">
         <f t="shared" si="6"/>
         <v>1597.4999999999995</v>
       </c>
-      <c r="S39" s="62">
+      <c r="S39" s="59">
         <f t="shared" si="7"/>
         <v>1910.3265867945152</v>
       </c>
     </row>
     <row r="40" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C40" s="3" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="D40" s="6">
         <f>(Bac_bb+Bac_bt)/2</f>
@@ -2713,9 +2599,9 @@
         <v>2</v>
       </c>
       <c r="M40" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="N40" s="63">
+        <v>92</v>
+      </c>
+      <c r="N40" s="60">
         <f>N23</f>
         <v>4500</v>
       </c>
@@ -2723,7 +2609,7 @@
         <f>FyPl/GammaM0</f>
         <v>355</v>
       </c>
-      <c r="P40" s="62">
+      <c r="P40" s="59">
         <f t="shared" si="4"/>
         <v>1597.5</v>
       </c>
@@ -2731,18 +2617,18 @@
         <f t="shared" si="5"/>
         <v>-7.5</v>
       </c>
-      <c r="R40" s="62">
+      <c r="R40" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S40" s="62">
+      <c r="S40" s="59">
         <f t="shared" si="7"/>
         <v>3507.8265867945152</v>
       </c>
     </row>
     <row r="41" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C41" s="3" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="D41" s="6">
         <v>50</v>
@@ -2765,13 +2651,13 @@
     </row>
     <row r="43" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C43" s="1" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="M43" s="3" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="N43" s="55">
         <f>P41</f>
@@ -2783,7 +2669,7 @@
     </row>
     <row r="45" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C45" s="3" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="D45" s="6">
         <v>350</v>
@@ -2792,14 +2678,14 @@
         <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C46" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D46" s="84">
+        <v>115</v>
+      </c>
+      <c r="D46" s="77">
         <f>td-Bac_Hp</f>
         <v>292</v>
       </c>
@@ -2834,11 +2720,17 @@
     </row>
     <row r="49" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C49" s="1" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
+      <c r="H49" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
     </row>
     <row r="50" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C50" s="3"/>
@@ -2846,16 +2738,26 @@
     </row>
     <row r="51" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C51" s="3" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="D51" s="6">
         <v>2500</v>
       </c>
       <c r="E51" t="s">
-        <v>101</v>
+        <v>65</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J51" s="98">
+        <f>dW</f>
+        <v>248.60000000000002</v>
+      </c>
+      <c r="K51" t="s">
+        <v>2</v>
       </c>
       <c r="N51" s="5" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="O51" s="5" t="s">
         <v>30</v>
@@ -2864,97 +2766,118 @@
         <v>32</v>
       </c>
       <c r="Q51" s="5" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C52" s="3"/>
       <c r="D52" s="4"/>
+      <c r="I52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J52" s="99">
+        <f>dW/tw</f>
+        <v>35.014084507042256</v>
+      </c>
       <c r="M52" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="N52" s="100">
+      <c r="N52" s="93">
         <f>P35</f>
         <v>569.77499999999998</v>
       </c>
-      <c r="O52" s="94">
+      <c r="O52" s="87">
         <f>Q35</f>
         <v>294.64999999999998</v>
       </c>
-      <c r="P52" s="74">
+      <c r="P52" s="67">
         <f>O52-zANP</f>
         <v>291.71266115685899</v>
       </c>
-      <c r="Q52" s="95">
+      <c r="Q52" s="88">
         <f>N52*ABS(P52/1000)</f>
         <v>166.21058151064935</v>
       </c>
     </row>
     <row r="53" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C53" s="3" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="D53" s="47">
         <f>(d_1+d_2)/2*tc*(1+Bac_bm*Bac_Hp/(Bac_e*tc))/1000</f>
         <v>0.62967149758454111</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>67</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J53" s="99">
+        <f>SQRT(235/FyW)</f>
+        <v>0.81361651346682706</v>
       </c>
       <c r="M53" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="N53" s="92">
+        <v>95</v>
+      </c>
+      <c r="N53" s="85">
         <f>P36</f>
         <v>72.090143397257634</v>
       </c>
-      <c r="O53" s="96">
+      <c r="O53" s="89">
         <f t="shared" ref="O53:O55" si="8">Q36</f>
         <v>285.94948091581375</v>
       </c>
-      <c r="P53" s="75">
+      <c r="P53" s="68">
         <f>O53-zANP</f>
         <v>283.01214207267276</v>
       </c>
-      <c r="Q53" s="97">
+      <c r="Q53" s="90">
         <f t="shared" ref="Q53:Q58" si="9">N53*ABS(P53/1000)</f>
         <v>20.40238590518403</v>
       </c>
     </row>
     <row r="54" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C54" s="3" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="D54" s="9">
         <f>Ac*rhoC</f>
         <v>1574.1787439613527</v>
       </c>
       <c r="E54" t="s">
-        <v>100</v>
+        <v>64</v>
+      </c>
+      <c r="I54" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="J54" s="99">
+        <f>38*J53</f>
+        <v>30.917427511739429</v>
       </c>
       <c r="M54" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="N54" s="92">
+      <c r="N54" s="85">
         <f t="shared" ref="N54:N55" si="10">P37</f>
         <v>626.59630000000004</v>
       </c>
-      <c r="O54" s="96">
+      <c r="O54" s="89">
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="P54" s="75">
+      <c r="P54" s="68">
         <f>O54-zANP</f>
         <v>147.06266115685901</v>
       </c>
-      <c r="Q54" s="97">
+      <c r="Q54" s="90">
         <f t="shared" si="9"/>
         <v>92.148919349041577</v>
       </c>
     </row>
     <row r="55" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C55" s="3" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D55" s="9">
         <f>D54*9.81/1000</f>
@@ -2963,22 +2886,29 @@
       <c r="E55" t="s">
         <v>7</v>
       </c>
+      <c r="I55" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="J55" s="98">
+        <f>IF(J54&gt;J52,2,3)</f>
+        <v>3</v>
+      </c>
       <c r="M55" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="N55" s="92">
+        <v>96</v>
+      </c>
+      <c r="N55" s="85">
         <f t="shared" si="10"/>
         <v>72.090143397257634</v>
       </c>
-      <c r="O55" s="96">
+      <c r="O55" s="89">
         <f t="shared" si="8"/>
         <v>14.050519084186226</v>
       </c>
-      <c r="P55" s="75">
+      <c r="P55" s="68">
         <f>O55-zANP</f>
         <v>11.113180241045239</v>
       </c>
-      <c r="Q55" s="97">
+      <c r="Q55" s="90">
         <f t="shared" si="9"/>
         <v>0.8011507571765214</v>
       </c>
@@ -2986,78 +2916,81 @@
     <row r="56" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C56" s="3"/>
       <c r="D56" s="4"/>
+      <c r="J56" s="4"/>
       <c r="M56" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="N56" s="92">
+        <v>129</v>
+      </c>
+      <c r="N56" s="85">
         <f>(1-pANP)*P39</f>
         <v>413.3617066027424</v>
       </c>
-      <c r="O56" s="96"/>
-      <c r="P56" s="75">
+      <c r="O56" s="89"/>
+      <c r="P56" s="68">
         <f>(1-pANP)*tf/2</f>
         <v>3.8813305784295062</v>
       </c>
-      <c r="Q56" s="97">
+      <c r="Q56" s="90">
         <f t="shared" si="9"/>
         <v>1.60439343178903</v>
       </c>
     </row>
     <row r="57" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C57" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D57" s="87">
+        <v>122</v>
+      </c>
+      <c r="D57" s="80">
         <f>9.81*(d_1+d_2)/2*Bac_Mu/1000</f>
         <v>0.22307939999999998</v>
       </c>
       <c r="E57" t="s">
         <v>7</v>
       </c>
-      <c r="M57" s="91" t="s">
-        <v>177</v>
-      </c>
-      <c r="N57" s="92">
+      <c r="J57" s="4"/>
+      <c r="M57" s="84" t="s">
+        <v>130</v>
+      </c>
+      <c r="N57" s="85">
         <f>pANP*P39</f>
         <v>156.41329339725758</v>
       </c>
-      <c r="O57" s="96"/>
-      <c r="P57" s="75">
+      <c r="O57" s="89"/>
+      <c r="P57" s="68">
         <f>(-pANP)*tf/2</f>
         <v>-1.4686694215704936</v>
       </c>
-      <c r="Q57" s="97">
+      <c r="Q57" s="90">
         <f t="shared" si="9"/>
         <v>0.22971942113968621</v>
       </c>
     </row>
     <row r="58" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C58" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D58" s="87">
+        <v>123</v>
+      </c>
+      <c r="D58" s="80">
         <f>V27*9.81/1000</f>
         <v>0.76093651749060698</v>
       </c>
       <c r="E58" t="s">
         <v>7</v>
       </c>
+      <c r="J58" s="4"/>
       <c r="M58" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="N58" s="101">
+        <v>92</v>
+      </c>
+      <c r="N58" s="94">
         <f>P40</f>
         <v>1597.5</v>
       </c>
-      <c r="O58" s="98">
+      <c r="O58" s="91">
         <f>Q40</f>
         <v>-7.5</v>
       </c>
-      <c r="P58" s="80">
+      <c r="P58" s="73">
         <f>O58-zANP</f>
         <v>-10.437338843140987</v>
       </c>
-      <c r="Q58" s="99">
+      <c r="Q58" s="92">
         <f t="shared" si="9"/>
         <v>16.673648801917725</v>
       </c>
@@ -3065,20 +2998,20 @@
     <row r="59" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C59" s="3"/>
       <c r="D59" s="4"/>
-      <c r="Q59" s="93">
+      <c r="Q59" s="86">
         <f>SUM(Q52:Q58)</f>
         <v>298.07079917689794</v>
       </c>
     </row>
     <row r="60" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C60" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D60" s="88">
+        <v>124</v>
+      </c>
+      <c r="D60" s="81">
         <f>SUM(D55,D57,D58)</f>
         <v>16.426709395751477</v>
       </c>
-      <c r="E60" s="59" t="s">
+      <c r="E60" s="57" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3088,7 +3021,7 @@
       <c r="P61" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Q61" s="83">
+      <c r="Q61" s="76">
         <f>Q59</f>
         <v>298.07079917689794</v>
       </c>
@@ -3100,9 +3033,9 @@
       <c r="C62" s="3"/>
       <c r="D62" s="4"/>
       <c r="P62" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q62" s="83">
+        <v>155</v>
+      </c>
+      <c r="Q62" s="76">
         <f>V26*FyW/SQRT(3)/1000/GammaM0</f>
         <v>526.37078127874736</v>
       </c>
@@ -3114,7 +3047,7 @@
       <c r="C63" s="3"/>
       <c r="D63" s="4"/>
       <c r="M63" s="2" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="N63" s="55">
         <f>SUM(N52:N56)</f>
@@ -3125,801 +3058,193 @@
       <c r="C64" s="3"/>
       <c r="D64" s="4"/>
       <c r="M64" s="2" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
       <c r="N64" s="55">
         <f>SUM(N57:N58)</f>
         <v>1753.9132933972576</v>
       </c>
     </row>
-    <row r="65" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C65" s="3"/>
       <c r="D65" s="4"/>
     </row>
-    <row r="66" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C66" s="3"/>
       <c r="D66" s="4"/>
     </row>
-    <row r="67" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C67" s="3"/>
       <c r="D67" s="4"/>
     </row>
-    <row r="68" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C68" s="3"/>
-      <c r="D68" s="4"/>
-      <c r="M68" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="N68" s="46"/>
-      <c r="O68" s="46"/>
-      <c r="P68" s="46"/>
-      <c r="Q68" s="46"/>
-      <c r="R68" s="46"/>
-      <c r="S68" s="46"/>
-    </row>
-    <row r="69" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C69" s="3"/>
-      <c r="D69" s="4"/>
-    </row>
-    <row r="70" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C70" s="3"/>
-      <c r="D70" s="4"/>
-      <c r="M70" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N70" s="8">
-        <f>Eta*hw*tw</f>
-        <v>2373.672</v>
-      </c>
-      <c r="O70" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="71" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C71" s="3"/>
-      <c r="D71" s="4"/>
+    <row r="68" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M68" s="3"/>
+      <c r="N68" s="4"/>
+    </row>
+    <row r="69" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M69" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="N69" s="62"/>
+      <c r="O69" s="63"/>
+      <c r="P69" s="63"/>
+      <c r="Q69" s="63"/>
+      <c r="R69" s="63"/>
+    </row>
+    <row r="70" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M70" s="3"/>
+      <c r="N70" s="4"/>
+    </row>
+    <row r="71" spans="3:18" x14ac:dyDescent="0.25">
       <c r="M71" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N71" s="5" t="e">
-        <f>(bf^3*tf+rr^3*tfi+hw*tw^3)/12/10^4</f>
-        <v>#NAME?</v>
+        <v>4</v>
+      </c>
+      <c r="N71" s="54">
+        <f>5/384*qG*LL^4/(E*IncertieCM/100)*1000^2</f>
+        <v>9.1389559152251394</v>
       </c>
       <c r="O71" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="72" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C72" s="3"/>
-      <c r="D72" s="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="3:18" x14ac:dyDescent="0.25">
       <c r="M72" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N72" s="6">
-        <v>7850</v>
+        <v>5</v>
+      </c>
+      <c r="N72" s="54">
+        <f>5/384*qQ_1*LL^4/(E*IncertieCM/100)*1000^2</f>
+        <v>11.126946602694259</v>
       </c>
       <c r="O72" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="73" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C73" s="3"/>
-      <c r="D73" s="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="3:18" x14ac:dyDescent="0.25">
       <c r="M73" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="N73" s="56">
-        <f>RhoA*A/(1000)^2</f>
-        <v>77.567432975597043</v>
+        <v>6</v>
+      </c>
+      <c r="N73" s="54">
+        <f>F_Q2*LL^3*1000/48/(E*IncertieCM/100)*1000</f>
+        <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C74" s="3"/>
-      <c r="D74" s="4"/>
-      <c r="M74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N74" s="65">
-        <f>N73*LL</f>
-        <v>465.40459785358223</v>
-      </c>
-      <c r="O74" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="75" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C75" s="3"/>
-      <c r="D75" s="4"/>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C76" s="57" t="s">
-        <v>52</v>
-      </c>
-      <c r="D76" s="57"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="57"/>
-      <c r="M76" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="N76" s="5">
-        <f>N77*LL/1000</f>
-        <v>5.6747999999999994</v>
-      </c>
-      <c r="O76" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="77" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C77" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D77" s="54">
-        <f>hw/tw</f>
-        <v>39.239436619718312</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="N77" s="5">
-        <f>2*Ht+2*bf-tw+2*rr-tw</f>
-        <v>945.8</v>
-      </c>
-      <c r="O77" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C78" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D78" s="5">
-        <f>zANP-tf</f>
-        <v>-7.7626611568590125</v>
-      </c>
-      <c r="E78" t="s">
+    <row r="74" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M74" s="3"/>
+      <c r="N74" s="4"/>
+    </row>
+    <row r="75" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M75" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N75" s="54">
+        <f>N71+N72+Psi_0*N73</f>
+        <v>20.2659025179194</v>
+      </c>
+      <c r="O75" t="s">
         <v>2</v>
       </c>
-      <c r="M78" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="N78" s="5">
-        <f>N76-(bf/1000*LL)</f>
-        <v>4.774799999999999</v>
-      </c>
-      <c r="O78" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="79" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C79" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D79" s="5" t="e">
-        <f>cc/hw</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M79" s="3"/>
-      <c r="N79" s="4"/>
-    </row>
-    <row r="80" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C80" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D80" s="52">
-        <f>SQRT(235/FyW)</f>
-        <v>0.81361651346682706</v>
-      </c>
-      <c r="M80" s="3"/>
-      <c r="N80" s="4"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C81" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D81" s="54" t="e">
-        <f>IF(Elan&lt;=0.5,36*EpsilonW/Alpha,396*EpsilonW/(13*Alpha-1))</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M81" s="3"/>
-      <c r="N81" s="4"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C82" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D82" s="54" t="e">
-        <f>IF(Elan&lt;=0.5,41.5*EpsilonW/Alpha,456*EpsilonW/(13*Alpha-1))</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M82" s="3"/>
-      <c r="N82" s="4"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C83" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D83" s="54" t="e">
-        <f>IF(Psi&lt;=-1,62*EpsilonW*(1-Psi)*SQRT(-Psi),42*espilonw/(0.67+0.33*Psi))</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M83" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="N83" s="68"/>
-      <c r="O83" s="69"/>
-      <c r="P83" s="69"/>
-      <c r="Q83" s="69"/>
-      <c r="R83" s="69"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="N76" s="4"/>
+    </row>
+    <row r="78" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M78" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="N78" s="62"/>
+      <c r="O78" s="63"/>
+      <c r="P78" s="63"/>
+      <c r="Q78" s="63"/>
+      <c r="R78" s="63"/>
+    </row>
+    <row r="79" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N79" s="5">
+        <v>9.81</v>
+      </c>
+      <c r="O79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M80" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N80" s="56">
+        <f>qG*LL/g*1000</f>
+        <v>10046.917061621698</v>
+      </c>
+      <c r="O80" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M81" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N81" s="56">
+        <f>qQ_1*LL/g*1000</f>
+        <v>12232.415902140672</v>
+      </c>
+      <c r="O81" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M82" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N82" s="65">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="83" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M83" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N83" s="56">
+        <f>N80+N82*N81</f>
+        <v>12493.400242049833</v>
+      </c>
+      <c r="O83" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84" spans="13:15" x14ac:dyDescent="0.25">
       <c r="M84" s="3"/>
       <c r="N84" s="4"/>
     </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C85" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D85" s="5" t="e">
-        <f>-(-zG-tf)/(Ht-tfi+zG)</f>
-        <v>#NAME?</v>
-      </c>
+    <row r="85" spans="13:15" x14ac:dyDescent="0.25">
       <c r="M85" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N85" s="54">
-        <f>5/384*qG*LL^4/(E*IncertieCM/100)*1000^2</f>
-        <v>9.1389559152251394</v>
+        <v>76</v>
+      </c>
+      <c r="N85" s="56">
+        <f>N83/2</f>
+        <v>6246.7001210249164</v>
       </c>
       <c r="O85" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="M86" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N86" s="54">
-        <f>5/384*qQ_1*LL^4/(E*IncertieCM/100)*1000^2</f>
-        <v>11.126946602694259</v>
-      </c>
-      <c r="O86" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C87" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D87" s="58" t="e">
-        <f>IF(Elan&lt;=D81,1,IF(Elan&lt;=D82,2,IF(Elan&lt;=D83,3,4)))</f>
-        <v>#NAME?</v>
-      </c>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="86" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M86" s="3"/>
+      <c r="N86" s="4"/>
+    </row>
+    <row r="87" spans="13:15" x14ac:dyDescent="0.25">
       <c r="M87" s="3" t="s">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="N87" s="54">
-        <f>F_Q2*LL^3*1000/48/(E*IncertieCM/100)*1000</f>
-        <v>0</v>
+        <f>1/2/PI()*SQRT(PI()^4*(E*IncertieCM/100)/N83/LL^3)</f>
+        <v>5.2662510823644419</v>
       </c>
       <c r="O87" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="M88" s="3"/>
-      <c r="N88" s="4"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="M89" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="N89" s="54">
-        <f>N85+N86+Psi_0*N87</f>
-        <v>20.2659025179194</v>
-      </c>
-      <c r="O89" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="N90" s="4"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="G91" s="60"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C92" s="60" t="s">
-        <v>62</v>
-      </c>
-      <c r="D92" s="60"/>
-      <c r="E92" s="60"/>
-      <c r="F92" s="60"/>
-      <c r="M92" s="70" t="s">
-        <v>110</v>
-      </c>
-      <c r="N92" s="68"/>
-      <c r="O92" s="69"/>
-      <c r="P92" s="69"/>
-      <c r="Q92" s="69"/>
-      <c r="R92" s="69"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="M93" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N93" s="5">
-        <v>9.81</v>
-      </c>
-      <c r="O93" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C94" s="59" t="s">
-        <v>63</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E94" s="55" t="e">
-        <f>IF(ClasseW=3,MelRd,MplRd)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="N94" s="56">
-        <f>qG*LL/g*1000</f>
-        <v>10046.917061621698</v>
-      </c>
-      <c r="O94" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="E95" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="N95" s="56">
-        <f>qQ_1*LL/g*1000</f>
-        <v>12232.415902140672</v>
-      </c>
-      <c r="O95" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D96" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E96" s="53" t="e">
-        <f>MEd_U1/MRd</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N96" s="71">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D97" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E97" s="53" t="e">
-        <f>MEd_U2/MRd</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="N97" s="56">
-        <f>N94+N96*N95</f>
-        <v>12493.400242049833</v>
-      </c>
-      <c r="O97" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D98" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E98" s="66" t="e">
-        <f>MAX(E96:E97)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="G98" s="73">
-        <f>VEd_U1/VRd</f>
-        <v>0.32173927864657914</v>
-      </c>
-      <c r="M98" s="3"/>
-      <c r="N98" s="4"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="M99" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N99" s="56">
-        <f>N97/2</f>
-        <v>6246.7001210249164</v>
-      </c>
-      <c r="O99" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C100" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E100" s="54">
-        <f>hw*tw*FyW/SQRT(3)/GammaM0/1000*Eta</f>
-        <v>486.50625969959651</v>
-      </c>
-      <c r="M100" s="3"/>
-      <c r="N100" s="4"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="E101" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="F101" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="N101" s="54">
-        <f>1/2/PI()*SQRT(PI()^4*(E*IncertieCM/100)/N97/LL^3)</f>
-        <v>5.2662510823644419</v>
-      </c>
-      <c r="O101" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D102" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E102" s="53">
-        <f>VEd_U1/VRd</f>
-        <v>0.32173927864657914</v>
-      </c>
-    </row>
-    <row r="103" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D103" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E103" s="53">
-        <f>VEd_U2/VRd</f>
-        <v>0.26624153434895853</v>
-      </c>
-    </row>
-    <row r="104" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D104" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E104" s="66">
-        <f>MAX(E102:E103)</f>
-        <v>0.32173927864657914</v>
-      </c>
-    </row>
-    <row r="106" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C106" s="59" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="107" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D107" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E107" s="54">
-        <f>hw/tw</f>
-        <v>39.239436619718312</v>
-      </c>
-    </row>
-    <row r="108" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D108" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E108" s="6">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="109" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D109" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E109" s="54">
-        <f>72*EpsilonW/Eta</f>
-        <v>48.816990808009628</v>
-      </c>
-    </row>
-    <row r="110" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D110" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E110" s="5" t="str">
-        <f>IF(ElancementW&gt;E109,oui,non)</f>
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="112" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D112" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E112" s="6">
-        <f>5.34</f>
-        <v>5.34</v>
-      </c>
-    </row>
-    <row r="113" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D113" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E113" s="64">
-        <f>ElancementW/(37.4*EpsilonW*SQRT(kTau))</f>
-        <v>0.55803415101238207</v>
-      </c>
-    </row>
-    <row r="114" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D114" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E114" s="47">
-        <f>IF(LambdaW&lt;=0.83/Eta,Eta,0.83/LambdaW)</f>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="115" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D115" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E115" s="48">
-        <f>KhiW*hw*tw*FyW/SQRT(3)/GammaM1/1000</f>
-        <v>486.50625969959651</v>
-      </c>
-    </row>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="F116" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="E117" s="63" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="118" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D118" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E118" s="53">
-        <f>VEd_U1/VbRd</f>
-        <v>0.32173927864657914</v>
-      </c>
-    </row>
-    <row r="119" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D119" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E119" s="53">
-        <f>VEd_U2/VbRd</f>
-        <v>0.26624153434895853</v>
-      </c>
-    </row>
-    <row r="120" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D120" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E120" s="66">
-        <f>MAX(E118:E119)</f>
-        <v>0.32173927864657914</v>
-      </c>
-    </row>
-    <row r="122" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C122" s="59" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="123" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D123" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E123" s="5">
-        <f>(bf*tf*(ABS(zG)-tf/2))/1000</f>
-        <v>117.04124460490951</v>
-      </c>
-    </row>
-    <row r="124" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C124" t="s">
-        <v>87</v>
-      </c>
-      <c r="F124" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="125" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D125" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E125" s="55">
-        <f>VEd_U1*(MStatS/IncertieCM)*100</f>
-        <v>126.83904667102597</v>
-      </c>
-      <c r="G125">
-        <f>Fu</f>
-        <v>470</v>
-      </c>
-    </row>
-    <row r="126" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D126" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E126" s="55">
-        <f>VEd_U2*(MStatS/IncertieCM)*100</f>
-        <v>104.96021046329331</v>
-      </c>
-      <c r="F126" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="127" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D127" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E127" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="F127" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D129" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E129" s="53">
-        <f>E125/Fu*GammaM2*SQRT(3)/2*BetaW</f>
-        <v>0.26292886422345124</v>
-      </c>
-    </row>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D130" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E130" s="53">
-        <f>E126/Fu*GammaM2*SQRT(3)/2*BetaW</f>
-        <v>0.2175754994228615</v>
-      </c>
-      <c r="F130" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="F131" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C133" s="59" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D134" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E134" s="5">
-        <v>4163.2</v>
-      </c>
-    </row>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D135" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E135" s="52" t="e">
-        <f>SQRT(MRd*GammaM0/Mcr)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="F135" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D136" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E136" s="6">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D137" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E137" s="53" t="e">
-        <f>0.5*(1+AlphaLT*(LambdaLT-0.2)+LambdaLT^2)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D138" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E138" s="61" t="e">
-        <f>1/(PhiLT+SQRT(PhiLT^2-LambdaLT^2))</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D139" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E139" s="55" t="e">
-        <f>KhiLT*MRd*GammaM0/GammaM1</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D140" s="3"/>
-      <c r="E140" s="4"/>
-      <c r="F140" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D141" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E141" s="66" t="e">
-        <f>MEd_U1/E139</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D142" s="3"/>
-      <c r="E142" s="4"/>
-    </row>
-    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D143" s="3"/>
-    </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C152" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D152" s="4">
-        <f>bf*tf*FyS/1000</f>
-        <v>569.77499999999998</v>
-      </c>
-    </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D153" s="4">
-        <f>hw*tw*FyW/1000</f>
-        <v>702.21130000000005</v>
-      </c>
-    </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D154" s="4" t="e">
-        <f>rr*tfi*FyI/1000</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D155" s="72" t="e">
-        <f>SUM(D152:D154)/GammaM0</f>
-        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
@@ -3938,29 +3263,29 @@
   <sheetData>
     <row r="2" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
@@ -3971,19 +3296,19 @@
         <f>hb</f>
         <v>300</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="79">
         <f t="shared" ref="E7:E12" si="0">1/(InertieY_MM4)*((zG-D7))*(10^3)</f>
         <v>-1.5351128617500458E-3</v>
       </c>
-      <c r="F7" s="85">
+      <c r="F7" s="78">
         <f t="shared" ref="F7:F12" si="1">MEd_U1*E7*1000</f>
         <v>-360.4326175193703</v>
       </c>
-      <c r="G7" s="73">
+      <c r="G7" s="100">
         <f t="shared" ref="G7:G12" si="2">ABS(F7/(FyS/GammaM0))</f>
         <v>1.0153031479418881</v>
       </c>
-      <c r="I7" s="82"/>
+      <c r="I7" s="75"/>
       <c r="J7" s="4"/>
       <c r="K7">
         <v>-113.47</v>
@@ -3997,15 +3322,15 @@
         <f>D7-tf</f>
         <v>289.3</v>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="79">
         <f t="shared" si="0"/>
         <v>-1.4610321239241081E-3</v>
       </c>
-      <c r="F8" s="85">
+      <c r="F8" s="78">
         <f t="shared" si="1"/>
         <v>-343.03903369392481</v>
       </c>
-      <c r="G8" s="73">
+      <c r="G8" s="100">
         <f t="shared" si="2"/>
         <v>0.96630713716598537</v>
       </c>
@@ -4017,19 +3342,19 @@
       <c r="C9" s="4">
         <v>3</v>
       </c>
-      <c r="D9" s="82">
+      <c r="D9" s="75">
         <f>zG</f>
         <v>78.272893834834576</v>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="85">
+      <c r="F9" s="78">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="73">
+      <c r="G9" s="100">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4046,15 +3371,15 @@
         <f>tf</f>
         <v>10.7</v>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="79">
         <f t="shared" si="0"/>
         <v>4.6783643292694458E-4</v>
       </c>
-      <c r="F10" s="85">
+      <c r="F10" s="78">
         <f t="shared" si="1"/>
         <v>109.84437320038558</v>
       </c>
-      <c r="G10" s="73">
+      <c r="G10" s="100">
         <f t="shared" si="2"/>
         <v>0.30942076957855091</v>
       </c>
@@ -4070,15 +3395,15 @@
       <c r="D11" s="4">
         <v>0</v>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="79">
         <f t="shared" si="0"/>
         <v>5.4191717075288237E-4</v>
       </c>
-      <c r="F11" s="85">
+      <c r="F11" s="78">
         <f t="shared" si="1"/>
         <v>127.23795702583109</v>
       </c>
-      <c r="G11" s="73">
+      <c r="G11" s="100">
         <f t="shared" si="2"/>
         <v>0.35841678035445379</v>
       </c>
@@ -4091,15 +3416,15 @@
         <f>-Pl_t</f>
         <v>-15</v>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="79">
         <f t="shared" si="0"/>
         <v>6.4576867237802881E-4</v>
       </c>
-      <c r="F12" s="85">
+      <c r="F12" s="78">
         <f t="shared" si="1"/>
         <v>151.62148575309118</v>
       </c>
-      <c r="G12" s="73">
+      <c r="G12" s="100">
         <f t="shared" si="2"/>
         <v>0.42710277676927094</v>
       </c>
@@ -4118,7 +3443,7 @@
     </row>
     <row r="15" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="D15" s="48">
         <f>2/3*bAppMin</f>
@@ -4132,19 +3457,19 @@
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D19" s="87">
+        <v>143</v>
+      </c>
+      <c r="D19" s="80">
         <f>(Pl_b-bf)/2-dApp</f>
         <v>41.666666666666671</v>
       </c>
@@ -4154,9 +3479,9 @@
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="87">
+        <v>145</v>
+      </c>
+      <c r="D20" s="80">
         <f>qELU*dp*6/Pl_t^2/2</f>
         <v>28.98669871348028</v>
       </c>
@@ -4166,14 +3491,14 @@
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C23" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" s="87">
+        <v>144</v>
+      </c>
+      <c r="D23" s="80">
         <f>(bf-tw)/2-rr</f>
         <v>56.45</v>
       </c>
@@ -4183,9 +3508,9 @@
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C24" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D24" s="87">
+        <v>145</v>
+      </c>
+      <c r="D24" s="80">
         <f>qELU*df*6/tf^2/2</f>
         <v>77.17718026753596</v>
       </c>
@@ -4195,161 +3520,161 @@
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D27" s="5" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>192</v>
+        <v>145</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="62">
+        <v>146</v>
+      </c>
+      <c r="D28" s="59">
         <f>F10</f>
         <v>109.84437320038558</v>
       </c>
-      <c r="E28" s="73">
+      <c r="E28" s="66">
         <f>+D24</f>
         <v>77.17718026753596</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
       </c>
-      <c r="G28" s="85">
+      <c r="G28" s="78">
         <f>SQRT(D28^2+E28^2-D28*E28+3*F28^2)</f>
         <v>97.696594034657494</v>
       </c>
-      <c r="H28" s="85">
+      <c r="H28" s="101">
         <f t="shared" ref="H28:H33" si="3">G28/(FyS/GammaM0)</f>
         <v>0.27520167333706336</v>
       </c>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C29" s="102" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="62">
+      <c r="C29" s="95" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="59">
         <f>AVERAGE(D28,D30)</f>
         <v>118.54116511310833</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
       </c>
-      <c r="F29" s="82">
+      <c r="F29" s="75">
         <f>3/2*qELU/tf/2</f>
         <v>3.6572003049718105</v>
       </c>
-      <c r="G29" s="85">
+      <c r="G29" s="78">
         <f t="shared" ref="G29:G33" si="4">SQRT(D29^2+E29^2-D29*E29+3*F29^2)</f>
         <v>118.7102909127312</v>
       </c>
-      <c r="H29" s="85">
+      <c r="H29" s="101">
         <f t="shared" si="3"/>
         <v>0.33439518566966536</v>
       </c>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C30" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="62">
+        <v>148</v>
+      </c>
+      <c r="D30" s="59">
         <f>F11</f>
         <v>127.23795702583109</v>
       </c>
-      <c r="E30" s="73">
+      <c r="E30" s="66">
         <f>-E28</f>
         <v>-77.17718026753596</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="85">
+      <c r="G30" s="78">
         <f t="shared" si="4"/>
         <v>178.78948964749171</v>
       </c>
-      <c r="H30" s="85">
+      <c r="H30" s="101">
         <f t="shared" si="3"/>
         <v>0.50363236520420196</v>
       </c>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C31" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31" s="62">
+        <v>149</v>
+      </c>
+      <c r="D31" s="59">
         <f>F11</f>
         <v>127.23795702583109</v>
       </c>
-      <c r="E31" s="73">
+      <c r="E31" s="66">
         <f>D20</f>
         <v>28.98669871348028</v>
       </c>
       <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="85">
+      <c r="G31" s="78">
         <f t="shared" si="4"/>
         <v>115.50548941581434</v>
       </c>
-      <c r="H31" s="85">
+      <c r="H31" s="101">
         <f t="shared" si="3"/>
         <v>0.32536757581919534</v>
       </c>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C32" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D32" s="62">
+        <v>150</v>
+      </c>
+      <c r="D32" s="59">
         <f>AVERAGE(D31,D33)</f>
         <v>139.42972138946112</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
       </c>
-      <c r="F32" s="73">
+      <c r="F32" s="66">
         <f>3/2*qELU/Pl_t/2</f>
         <v>2.6088028842132247</v>
       </c>
-      <c r="G32" s="85">
+      <c r="G32" s="78">
         <f t="shared" si="4"/>
         <v>139.50292027125738</v>
       </c>
-      <c r="H32" s="85">
+      <c r="H32" s="101">
         <f t="shared" si="3"/>
         <v>0.3929659725950912</v>
       </c>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C33" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D33" s="62">
+        <v>151</v>
+      </c>
+      <c r="D33" s="59">
         <f>F12</f>
         <v>151.62148575309118</v>
       </c>
-      <c r="E33" s="73">
+      <c r="E33" s="66">
         <f>-E31</f>
         <v>-28.98669871348028</v>
       </c>
       <c r="F33" s="4">
         <v>0</v>
       </c>
-      <c r="G33" s="85">
+      <c r="G33" s="78">
         <f t="shared" si="4"/>
         <v>168.00092252810995</v>
       </c>
-      <c r="H33" s="85">
+      <c r="H33" s="101">
         <f t="shared" si="3"/>
         <v>0.47324203529045056</v>
       </c>
